--- a/conformance/fixtures/043-ifempty-function/template.xlsx
+++ b/conformance/fixtures/043-ifempty-function/template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
+    <sheet sheetId="1" name="__config__" state="hidden" r:id="rId4"/>
     <sheet sheetId="2" name="Report" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
